--- a/pandas_stock/stock_data_2026_6.xlsx
+++ b/pandas_stock/stock_data_2026_6.xlsx
@@ -1847,7 +1847,7 @@
         <v>46246</v>
       </c>
       <c r="B51">
-        <v>15.89</v>
+        <v>25.89</v>
       </c>
     </row>
     <row r="52" spans="1:2">
